--- a/Rocket-Nose-Cone/Rocket data.xlsx
+++ b/Rocket-Nose-Cone/Rocket data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{A8C71B2D-CA63-43E0-BAB5-8DF1FBFFB579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CB70F96-914A-4E92-A8C3-43A74DCF095C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{737AA5AF-92CE-4977-868D-A9FAC096875E}"/>
+    <workbookView xWindow="7440" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{737AA5AF-92CE-4977-868D-A9FAC096875E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
